--- a/stat571B_reading_data.xlsx
+++ b/stat571B_reading_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/caroline/Downloads/Stat 571B/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1619D4E-09E1-40E9-9779-C6323953CF7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{19ECB948-5A85-4C64-9471-B3280F20505C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="740" windowWidth="28040" windowHeight="17160" xr2:uid="{075105F4-FEEB-E240-A560-849AF48E5476}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -124,6 +124,12 @@
       <name val="Aptos Narrow"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -145,11 +151,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -518,7 +525,15 @@
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" s="1"/>
+      <c r="C2" s="4">
+        <v>100</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>17</v>
+      </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
@@ -527,6 +542,15 @@
       <c r="B3">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>75</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>45</v>
+      </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
@@ -535,6 +559,15 @@
       <c r="B4">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>75</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>58</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
@@ -543,6 +576,15 @@
       <c r="B5">
         <v>1</v>
       </c>
+      <c r="C5">
+        <v>75</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>14</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
@@ -551,6 +593,15 @@
       <c r="B6" s="2">
         <v>2</v>
       </c>
+      <c r="C6">
+        <v>50</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>36</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
@@ -559,6 +610,15 @@
       <c r="B7" s="2">
         <v>3</v>
       </c>
+      <c r="C7">
+        <v>75</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>51</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
@@ -567,6 +627,15 @@
       <c r="B8">
         <v>1</v>
       </c>
+      <c r="C8">
+        <v>75</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
@@ -575,6 +644,15 @@
       <c r="B9" s="2">
         <v>2</v>
       </c>
+      <c r="C9">
+        <v>100</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>28</v>
+      </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
@@ -582,6 +660,15 @@
       </c>
       <c r="B10" s="2">
         <v>3</v>
+      </c>
+      <c r="C10">
+        <v>75</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:6">
